--- a/tumores/3. Orofaringe (p16+).xlsx
+++ b/tumores/3. Orofaringe (p16+).xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Ing.Salud\Practicas hospital ORL\Proyecto Practicas\tumores\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Ing.Salud\Practicas hospital ORL\clasificador-tnm-cabeza-cuello\tumores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED3D0BEB-2DF0-45CD-9ABE-BA776787518F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DB7E1A4-8CF9-4F70-BBCF-7A98571BA1E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14520" yWindow="0" windowWidth="8520" windowHeight="8880" xr2:uid="{4CA4EF29-18F6-42B8-89A4-4F1C5D6105C8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4CA4EF29-18F6-42B8-89A4-4F1C5D6105C8}"/>
   </bookViews>
   <sheets>
     <sheet name="TNM" sheetId="1" r:id="rId1"/>
@@ -79,15 +79,9 @@
     <t>Ganglios no evaluables</t>
   </si>
   <si>
-    <t>Ganglio ipsilateral ≤3 cm y ENE-</t>
-  </si>
-  <si>
     <t>Sin metástasis en ganglios</t>
   </si>
   <si>
-    <t xml:space="preserve"> ENE+: </t>
-  </si>
-  <si>
     <t>M</t>
   </si>
   <si>
@@ -109,9 +103,6 @@
     <t>&gt;2 cm y ≤4 cm</t>
   </si>
   <si>
-    <t>Ganglios contralaterales ≤6 cm</t>
-  </si>
-  <si>
     <t>Sin metástasis</t>
   </si>
   <si>
@@ -142,21 +133,12 @@
     <t>Laringe, Músculo extrínseco de la lengua, Músculo pterigoideo medio, Paladar duro, Maxilar inferior, Otras partes</t>
   </si>
   <si>
-    <t>Ganglio ipsilateral ≤6 cm</t>
-  </si>
-  <si>
     <t>Uno, Varios</t>
   </si>
   <si>
-    <t>Ganglio contralateral  ≤6 cm</t>
-  </si>
-  <si>
     <t>N2</t>
   </si>
   <si>
-    <t>Ganglio bilateral  ≤6 cm</t>
-  </si>
-  <si>
     <t>N3</t>
   </si>
   <si>
@@ -202,30 +184,15 @@
     <t>N0: Ganglios sin metástasis</t>
   </si>
   <si>
-    <t>🟨 N2: Ganglio contralateral  ≤6 cm</t>
-  </si>
-  <si>
-    <t>🟨 N2: Ganglio bilateral  ≤6 cm</t>
-  </si>
-  <si>
     <t>🟦 N3: Ganglios &gt;6 cm</t>
   </si>
   <si>
-    <t>🟩 N1: Metastasis en 4 o menos ganglios</t>
-  </si>
-  <si>
-    <t>🟨 N2: Metastasis en más de 4 ganglios</t>
-  </si>
-  <si>
     <t>M0: Sin metástasis a distancia</t>
   </si>
   <si>
     <t>M1: Metástasis a distancia</t>
   </si>
   <si>
-    <t>🟩 N1: Ganglio ipsilateral ≤6 cm *</t>
-  </si>
-  <si>
     <t xml:space="preserve">Inv: </t>
   </si>
   <si>
@@ -245,6 +212,39 @@
   </si>
   <si>
     <t>N2, pN2</t>
+  </si>
+  <si>
+    <t>Ganglios &gt;6 cm</t>
+  </si>
+  <si>
+    <t>Metástasis en 4 o menos ganglios</t>
+  </si>
+  <si>
+    <t>Metástasis en más de 4 ganglios</t>
+  </si>
+  <si>
+    <t>🟩 N1: Ganglios ipsilateral ≤6 cm *</t>
+  </si>
+  <si>
+    <t>Ganglios ipsilaterales ≤6 cm</t>
+  </si>
+  <si>
+    <t>Ganglios contralaterales  ≤6 cm</t>
+  </si>
+  <si>
+    <t>Ganglios bilaterales  ≤6 cm</t>
+  </si>
+  <si>
+    <t>🟨 N2: Ganglios bilaterales  ≤6 cm</t>
+  </si>
+  <si>
+    <t>🟨 N2: Ganglios contralaterales  ≤6 cm</t>
+  </si>
+  <si>
+    <t>🟩 N1: Metástasis en 4 o menos ganglios</t>
+  </si>
+  <si>
+    <t>🟨 N2: Metástasis en más de 4 ganglios</t>
   </si>
 </sst>
 </file>
@@ -773,7 +773,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>6</v>
@@ -782,7 +782,7 @@
         <v>9</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>7</v>
@@ -794,11 +794,11 @@
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>4</v>
@@ -810,14 +810,14 @@
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
         <v>1</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -826,14 +826,14 @@
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -842,7 +842,7 @@
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
@@ -858,14 +858,14 @@
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -874,16 +874,16 @@
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="6" t="s">
         <v>55</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -894,7 +894,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>13</v>
@@ -911,13 +911,13 @@
         <v>11</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>14</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -931,13 +931,13 @@
         <v>65</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -948,13 +948,13 @@
         <v>11</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>40</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -965,13 +965,13 @@
         <v>11</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -982,13 +982,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -999,7 +999,7 @@
         <v>12</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>13</v>
@@ -1016,13 +1016,13 @@
         <v>12</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>14</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -1033,13 +1033,13 @@
         <v>12</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1050,42 +1050,42 @@
         <v>12</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="D17" s="7"/>
       <c r="E17" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>19</v>
+        <v>58</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E19" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>22</v>
-      </c>
       <c r="F19" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -1114,38 +1114,38 @@
         <v>10</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -1153,83 +1153,83 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/tumores/3. Orofaringe (p16+).xlsx
+++ b/tumores/3. Orofaringe (p16+).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Ing.Salud\Practicas hospital ORL\clasificador-tnm-cabeza-cuello\tumores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DB7E1A4-8CF9-4F70-BBCF-7A98571BA1E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9640DBE1-8453-4469-B5EB-585F410F89E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4CA4EF29-18F6-42B8-89A4-4F1C5D6105C8}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="72">
   <si>
     <t>T</t>
   </si>
@@ -130,9 +130,6 @@
     <t>T4</t>
   </si>
   <si>
-    <t>Laringe, Músculo extrínseco de la lengua, Músculo pterigoideo medio, Paladar duro, Maxilar inferior, Otras partes</t>
-  </si>
-  <si>
     <t>Uno, Varios</t>
   </si>
   <si>
@@ -175,9 +172,6 @@
     <t>🟦 T3: Diseminación de superficie lingual de la epiglotis</t>
   </si>
   <si>
-    <t>🟥 T4: Invasión *</t>
-  </si>
-  <si>
     <t>NX: Ganglios no evaluables</t>
   </si>
   <si>
@@ -193,9 +187,6 @@
     <t>M1: Metástasis a distancia</t>
   </si>
   <si>
-    <t xml:space="preserve">Inv: </t>
-  </si>
-  <si>
     <t>Diseminación de superficie lingual de la epiglotis</t>
   </si>
   <si>
@@ -245,6 +236,12 @@
   </si>
   <si>
     <t>🟨 N2: Metástasis en más de 4 ganglios</t>
+  </si>
+  <si>
+    <t>🟥 T4: Enfermedad localmente avanzada *</t>
+  </si>
+  <si>
+    <t>Invasión de Laringe, Invasión del Músculo extrínseco de la lengua, Invasión del Músculo pterigoideo medio, Invasión del Paladar duro, Invasión de Mandíbula, Invasión de otras partes</t>
   </si>
 </sst>
 </file>
@@ -761,8 +758,8 @@
   <cols>
     <col min="1" max="1" width="9" style="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.33203125" style="5" customWidth="1"/>
-    <col min="3" max="3" width="35.33203125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="27.88671875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="36.6640625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="39.77734375" style="5" customWidth="1"/>
     <col min="5" max="5" width="27.21875" style="5" customWidth="1"/>
     <col min="6" max="6" width="38.44140625" style="5" customWidth="1"/>
     <col min="7" max="16384" width="11.5546875" style="5"/>
@@ -794,7 +791,7 @@
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="1" t="s">
@@ -810,7 +807,7 @@
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
@@ -826,7 +823,7 @@
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
@@ -842,7 +839,7 @@
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
@@ -858,33 +855,31 @@
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="6" t="s">
-        <v>55</v>
-      </c>
+      <c r="F7" s="6"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
@@ -894,7 +889,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>13</v>
@@ -911,7 +906,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>14</v>
@@ -928,16 +923,16 @@
         <v>11</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -948,13 +943,13 @@
         <v>11</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -965,13 +960,13 @@
         <v>11</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -982,13 +977,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -999,7 +994,7 @@
         <v>12</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>13</v>
@@ -1016,7 +1011,7 @@
         <v>12</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>14</v>
@@ -1033,13 +1028,13 @@
         <v>12</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1050,14 +1045,14 @@
         <v>12</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D17" s="7"/>
       <c r="E17" s="6" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -1065,7 +1060,7 @@
         <v>18</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>19</v>
@@ -1079,7 +1074,7 @@
         <v>18</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>20</v>
@@ -1122,10 +1117,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>19</v>
@@ -1136,10 +1131,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>19</v>
@@ -1153,7 +1148,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>19</v>
@@ -1164,10 +1159,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>19</v>
@@ -1181,7 +1176,7 @@
         <v>33</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>19</v>
@@ -1192,10 +1187,10 @@
     </row>
     <row r="7" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>19</v>
@@ -1206,10 +1201,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>19</v>
@@ -1229,7 +1224,7 @@
         <v>20</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/tumores/3. Orofaringe (p16+).xlsx
+++ b/tumores/3. Orofaringe (p16+).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Ing.Salud\Practicas hospital ORL\clasificador-tnm-cabeza-cuello\tumores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9640DBE1-8453-4469-B5EB-585F410F89E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{400BE703-7D67-4E00-89AA-E0EC68706D54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4CA4EF29-18F6-42B8-89A4-4F1C5D6105C8}"/>
   </bookViews>
@@ -241,7 +241,7 @@
     <t>🟥 T4: Enfermedad localmente avanzada *</t>
   </si>
   <si>
-    <t>Invasión de Laringe, Invasión del Músculo extrínseco de la lengua, Invasión del Músculo pterigoideo medio, Invasión del Paladar duro, Invasión de Mandíbula, Invasión de otras partes</t>
+    <t>Invasión de laringe, Invasión del músculo extrínseco de la lengua, Invasión del músculo pterigoideo medio, Invasión del paladar duro, Invasión de mandíbula, Invasión de otras partes</t>
   </si>
 </sst>
 </file>
